--- a/data/dimensions/dim_tiempo.xlsx
+++ b/data/dimensions/dim_tiempo.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\snies-spadies-etl\data\dimensions\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\snies-spadies-etl\data\dimensions\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{998FA471-52EF-4CBD-8623-AAA469C5D9E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13860" windowHeight="6030"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -346,8 +347,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B57"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -360,7 +361,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>1999</v>
+        <v>2015</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -368,7 +369,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>1999</v>
+        <v>2015</v>
       </c>
       <c r="B3">
         <v>2</v>
@@ -376,7 +377,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>2000</v>
+        <v>2016</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -384,7 +385,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>2000</v>
+        <v>2016</v>
       </c>
       <c r="B5">
         <v>2</v>
@@ -392,7 +393,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>2001</v>
+        <v>2017</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -400,7 +401,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>2001</v>
+        <v>2017</v>
       </c>
       <c r="B7">
         <v>2</v>
@@ -408,7 +409,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>2002</v>
+        <v>2018</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -416,7 +417,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>2002</v>
+        <v>2018</v>
       </c>
       <c r="B9">
         <v>2</v>
@@ -424,7 +425,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>2003</v>
+        <v>2019</v>
       </c>
       <c r="B10">
         <v>1</v>
@@ -432,7 +433,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>2003</v>
+        <v>2019</v>
       </c>
       <c r="B11">
         <v>2</v>
@@ -440,7 +441,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>2004</v>
+        <v>2020</v>
       </c>
       <c r="B12">
         <v>1</v>
@@ -448,7 +449,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>2004</v>
+        <v>2020</v>
       </c>
       <c r="B13">
         <v>2</v>
@@ -456,7 +457,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>2005</v>
+        <v>2021</v>
       </c>
       <c r="B14">
         <v>1</v>
@@ -464,7 +465,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>2005</v>
+        <v>2021</v>
       </c>
       <c r="B15">
         <v>2</v>
@@ -472,7 +473,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>2006</v>
+        <v>2022</v>
       </c>
       <c r="B16">
         <v>1</v>
@@ -480,7 +481,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>2006</v>
+        <v>2022</v>
       </c>
       <c r="B17">
         <v>2</v>
@@ -488,7 +489,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>2007</v>
+        <v>2023</v>
       </c>
       <c r="B18">
         <v>1</v>
@@ -496,7 +497,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>2007</v>
+        <v>2023</v>
       </c>
       <c r="B19">
         <v>2</v>
@@ -504,7 +505,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>2008</v>
+        <v>2024</v>
       </c>
       <c r="B20">
         <v>1</v>
@@ -512,297 +513,9 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>2008</v>
+        <v>2024</v>
       </c>
       <c r="B21">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22">
-        <v>2009</v>
-      </c>
-      <c r="B22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23">
-        <v>2009</v>
-      </c>
-      <c r="B23">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24">
-        <v>2010</v>
-      </c>
-      <c r="B24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25">
-        <v>2010</v>
-      </c>
-      <c r="B25">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26">
-        <v>2011</v>
-      </c>
-      <c r="B26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27">
-        <v>2011</v>
-      </c>
-      <c r="B27">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28">
-        <v>2012</v>
-      </c>
-      <c r="B28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29">
-        <v>2012</v>
-      </c>
-      <c r="B29">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30">
-        <v>2013</v>
-      </c>
-      <c r="B30">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31">
-        <v>2013</v>
-      </c>
-      <c r="B31">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32">
-        <v>2014</v>
-      </c>
-      <c r="B32">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33">
-        <v>2014</v>
-      </c>
-      <c r="B33">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34">
-        <v>2015</v>
-      </c>
-      <c r="B34">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35">
-        <v>2015</v>
-      </c>
-      <c r="B35">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36">
-        <v>2016</v>
-      </c>
-      <c r="B36">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37">
-        <v>2016</v>
-      </c>
-      <c r="B37">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38">
-        <v>2017</v>
-      </c>
-      <c r="B38">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39">
-        <v>2017</v>
-      </c>
-      <c r="B39">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40">
-        <v>2018</v>
-      </c>
-      <c r="B40">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41">
-        <v>2018</v>
-      </c>
-      <c r="B41">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42">
-        <v>2019</v>
-      </c>
-      <c r="B42">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43">
-        <v>2019</v>
-      </c>
-      <c r="B43">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44">
-        <v>2020</v>
-      </c>
-      <c r="B44">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45">
-        <v>2020</v>
-      </c>
-      <c r="B45">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46">
-        <v>2021</v>
-      </c>
-      <c r="B46">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47">
-        <v>2021</v>
-      </c>
-      <c r="B47">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48">
-        <v>2022</v>
-      </c>
-      <c r="B48">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49">
-        <v>2022</v>
-      </c>
-      <c r="B49">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50">
-        <v>2023</v>
-      </c>
-      <c r="B50">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51">
-        <v>2023</v>
-      </c>
-      <c r="B51">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52">
-        <v>2024</v>
-      </c>
-      <c r="B52">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A53">
-        <v>2024</v>
-      </c>
-      <c r="B53">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54">
-        <v>2025</v>
-      </c>
-      <c r="B54">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A55">
-        <v>2025</v>
-      </c>
-      <c r="B55">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A56">
-        <v>2026</v>
-      </c>
-      <c r="B56">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A57">
-        <v>2026</v>
-      </c>
-      <c r="B57">
         <v>2</v>
       </c>
     </row>
